--- a/Carnitas_Costeo_Boyaca.xlsx
+++ b/Carnitas_Costeo_Boyaca.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\GitHub\carnitas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9AF65348-634A-4CB9-BFF7-991FEDB0C379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C2CE8EE-156E-452E-9777-67B702C57D6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AB8337B3-0B0D-475D-9695-5DD86729B17B}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="156">
   <si>
     <t>Carnitas — Costeo del menú para Boyacá</t>
   </si>
@@ -88,9 +88,6 @@
     <t>Las ganancias son brutas: no incluyen arriendo, nómina, servicios ni comisiones de apps.</t>
   </si>
   <si>
-    <t>EL MENÚ: 3 PLATOS, 2 TAMAÑOS (personal y para compartir)</t>
-  </si>
-  <si>
     <t>1. La Clásica Carnitas — motor de recompra y precio de entrada.</t>
   </si>
   <si>
@@ -500,6 +497,21 @@
   </si>
   <si>
     <t>• Clima frío: combos con aguapanela o chocolate.</t>
+  </si>
+  <si>
+    <t>4. La Tocinetuda</t>
+  </si>
+  <si>
+    <t>Opción económica y sencilla: papa, queso, tocineta y Salsa Carnitas. Precio de entrada para estudiantes.</t>
+  </si>
+  <si>
+    <t>La Tocinetuda</t>
+  </si>
+  <si>
+    <t>4. La Tocinetuda — opción económica: papa, queso, tocineta y Salsa Carnitas.</t>
+  </si>
+  <si>
+    <t>EL MENÚ: 4 PLATOS, 2 TAMAÑOS (personal y para compartir)</t>
   </si>
 </sst>
 </file>
@@ -970,7 +982,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8CFB703-E291-4D77-A203-FAF6BF6FCE10}">
-  <dimension ref="A1:A40"/>
+  <dimension ref="A1:A41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="120.77734375" style="1" customWidth="1"/>
@@ -1049,97 +1061,102 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>14</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1149,7 +1166,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EE1B1F4-2B19-4169-B08C-B72E24B838B5}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.77734375" style="1" customWidth="1"/>
@@ -1166,66 +1183,66 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B3" s="13">
         <v>0.35</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B4" s="13">
         <v>0.25</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>121</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>124</v>
       </c>
       <c r="C7" s="20">
         <f>'Fichas técnicas'!C16</f>
@@ -1239,28 +1256,28 @@
         <v>18900</v>
       </c>
       <c r="F7" s="12">
-        <f>IF(E7=0,0,D7/E7)</f>
+        <f t="shared" ref="F7:F12" si="0">IF(E7=0,0,D7/E7)</f>
         <v>0.39137136450197269</v>
       </c>
       <c r="G7" s="7">
-        <f>E7-D7</f>
+        <f t="shared" ref="G7:G12" si="1">E7-D7</f>
         <v>11503.081210912716</v>
       </c>
       <c r="H7" s="7">
-        <f>IF($B$3=0,0,CEILING(D7/$B$3,1000)-100)</f>
+        <f t="shared" ref="H7:H12" si="2">IF($B$3=0,0,CEILING(D7/$B$3,1000)-100)</f>
         <v>21900</v>
       </c>
       <c r="I7" s="7">
-        <f>IF($B$4&gt;=1,0,CEILING(E7/(1-$B$4),1000)-100)</f>
+        <f t="shared" ref="I7:I12" si="3">IF($B$4&gt;=1,0,CEILING(E7/(1-$B$4),1000)-100)</f>
         <v>25900</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" s="20">
         <f>'Fichas técnicas'!E16</f>
@@ -1274,28 +1291,28 @@
         <v>36900</v>
       </c>
       <c r="F8" s="12">
-        <f>IF(E8=0,0,D8/E8)</f>
+        <f t="shared" si="0"/>
         <v>0.38736687203725112</v>
       </c>
       <c r="G8" s="7">
-        <f>E8-D8</f>
+        <f t="shared" si="1"/>
         <v>22606.162421825433</v>
       </c>
       <c r="H8" s="7">
-        <f>IF($B$3=0,0,CEILING(D8/$B$3,1000)-100)</f>
+        <f t="shared" si="2"/>
         <v>40900</v>
       </c>
       <c r="I8" s="7">
-        <f>IF($B$4&gt;=1,0,CEILING(E8/(1-$B$4),1000)-100)</f>
+        <f t="shared" si="3"/>
         <v>49900</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C9" s="20">
         <f>'Fichas técnicas'!C32</f>
@@ -1309,28 +1326,28 @@
         <v>26900</v>
       </c>
       <c r="F9" s="12">
-        <f>IF(E9=0,0,D9/E9)</f>
+        <f t="shared" si="0"/>
         <v>0.34720168659280692</v>
       </c>
       <c r="G9" s="7">
-        <f>E9-D9</f>
+        <f t="shared" si="1"/>
         <v>17560.274630653494</v>
       </c>
       <c r="H9" s="7">
-        <f>IF($B$3=0,0,CEILING(D9/$B$3,1000)-100)</f>
+        <f t="shared" si="2"/>
         <v>26900</v>
       </c>
       <c r="I9" s="7">
-        <f>IF($B$4&gt;=1,0,CEILING(E9/(1-$B$4),1000)-100)</f>
+        <f t="shared" si="3"/>
         <v>35900</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C10" s="20">
         <f>'Fichas técnicas'!E32</f>
@@ -1344,28 +1361,28 @@
         <v>47900</v>
       </c>
       <c r="F10" s="12">
-        <f>IF(E10=0,0,D10/E10)</f>
+        <f t="shared" si="0"/>
         <v>0.37952924297897728</v>
       </c>
       <c r="G10" s="7">
-        <f>E10-D10</f>
+        <f t="shared" si="1"/>
         <v>29720.549261306987</v>
       </c>
       <c r="H10" s="7">
-        <f>IF($B$3=0,0,CEILING(D10/$B$3,1000)-100)</f>
+        <f t="shared" si="2"/>
         <v>51900</v>
       </c>
       <c r="I10" s="7">
-        <f>IF($B$4&gt;=1,0,CEILING(E10/(1-$B$4),1000)-100)</f>
+        <f t="shared" si="3"/>
         <v>63900</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C11" s="20">
         <f>'Fichas técnicas'!C49</f>
@@ -1379,28 +1396,28 @@
         <v>27900</v>
       </c>
       <c r="F11" s="12">
-        <f>IF(E11=0,0,D11/E11)</f>
+        <f t="shared" si="0"/>
         <v>0.37031788207943955</v>
       </c>
       <c r="G11" s="7">
-        <f>E11-D11</f>
+        <f t="shared" si="1"/>
         <v>17568.131089983639</v>
       </c>
       <c r="H11" s="7">
-        <f>IF($B$3=0,0,CEILING(D11/$B$3,1000)-100)</f>
+        <f t="shared" si="2"/>
         <v>29900</v>
       </c>
       <c r="I11" s="7">
-        <f>IF($B$4&gt;=1,0,CEILING(E11/(1-$B$4),1000)-100)</f>
+        <f t="shared" si="3"/>
         <v>37900</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C12" s="20">
         <f>'Fichas técnicas'!E49</f>
@@ -1414,40 +1431,110 @@
         <v>49900</v>
       </c>
       <c r="F12" s="12">
-        <f>IF(E12=0,0,D12/E12)</f>
+        <f t="shared" si="0"/>
         <v>0.4040829222451448</v>
       </c>
       <c r="G12" s="7">
-        <f>E12-D12</f>
+        <f t="shared" si="1"/>
         <v>29736.262179967274</v>
       </c>
       <c r="H12" s="7">
-        <f>IF($B$3=0,0,CEILING(D12/$B$3,1000)-100)</f>
+        <f t="shared" si="2"/>
         <v>57900</v>
       </c>
       <c r="I12" s="7">
-        <f>IF($B$4&gt;=1,0,CEILING(E12/(1-$B$4),1000)-100)</f>
+        <f t="shared" si="3"/>
         <v>66900</v>
       </c>
     </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" s="20">
+        <f>'Fichas técnicas'!C62</f>
+        <v>350</v>
+      </c>
+      <c r="D13" s="15">
+        <f>'Fichas técnicas'!D62</f>
+        <v>4796.9187890872836</v>
+      </c>
+      <c r="E13" s="8">
+        <v>12900</v>
+      </c>
+      <c r="F13" s="12">
+        <f>IF(E13=0,0,D13/E13)</f>
+        <v>0.37185416969668866</v>
+      </c>
+      <c r="G13" s="7">
+        <f>E13-D13</f>
+        <v>8103.0812109127164</v>
+      </c>
+      <c r="H13" s="7">
+        <f>IF($B$3=0,0,CEILING(D13/$B$3,1000)-100)</f>
+        <v>13900</v>
+      </c>
+      <c r="I13" s="7">
+        <f>IF($B$4&gt;=1,0,CEILING(E13/(1-$B$4),1000)-100)</f>
+        <v>17900</v>
+      </c>
+    </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>129</v>
+      <c r="A14" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" s="20">
+        <f>'Fichas técnicas'!E62</f>
+        <v>700</v>
+      </c>
+      <c r="D14" s="15">
+        <f>'Fichas técnicas'!F62</f>
+        <v>9093.8375781745672</v>
+      </c>
+      <c r="E14" s="8">
+        <v>23900</v>
+      </c>
+      <c r="F14" s="12">
+        <f>IF(E14=0,0,D14/E14)</f>
+        <v>0.38049529615793171</v>
+      </c>
+      <c r="G14" s="7">
+        <f>E14-D14</f>
+        <v>14806.162421825433</v>
+      </c>
+      <c r="H14" s="7">
+        <f>IF($B$3=0,0,CEILING(D14/$B$3,1000)-100)</f>
+        <v>25900</v>
+      </c>
+      <c r="I14" s="7">
+        <f>IF($B$4&gt;=1,0,CEILING(E14/(1-$B$4),1000)-100)</f>
+        <v>31900</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>130</v>
+      <c r="A16" s="2" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -1457,7 +1544,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3C62A82-7C7F-4FFC-8968-8AB6A197D1DB}">
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.77734375" style="1" customWidth="1"/>
@@ -1471,12 +1558,12 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -1487,35 +1574,35 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B6" s="18" t="str">
         <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A6,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
@@ -1525,14 +1612,14 @@
         <v>250</v>
       </c>
       <c r="D6" s="7">
-        <f>C6*G6</f>
+        <f t="shared" ref="D6:D15" si="0">C6*G6</f>
         <v>727.27272727272725</v>
       </c>
       <c r="E6" s="6">
         <v>500</v>
       </c>
       <c r="F6" s="7">
-        <f>E6*G6</f>
+        <f t="shared" ref="F6:F15" si="1">E6*G6</f>
         <v>1454.5454545454545</v>
       </c>
       <c r="G6" s="19">
@@ -1542,7 +1629,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B7" s="18" t="str">
         <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A7,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
@@ -1552,14 +1639,14 @@
         <v>1</v>
       </c>
       <c r="D7" s="7">
-        <f>C7*G7</f>
+        <f t="shared" si="0"/>
         <v>500</v>
       </c>
       <c r="E7" s="6">
         <v>2</v>
       </c>
       <c r="F7" s="7">
-        <f>E7*G7</f>
+        <f t="shared" si="1"/>
         <v>1000</v>
       </c>
       <c r="G7" s="19">
@@ -1569,7 +1656,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B8" s="18" t="str">
         <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A8,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
@@ -1579,14 +1666,14 @@
         <v>60</v>
       </c>
       <c r="D8" s="7">
-        <f>C8*G8</f>
+        <f t="shared" si="0"/>
         <v>2040</v>
       </c>
       <c r="E8" s="6">
         <v>120</v>
       </c>
       <c r="F8" s="7">
-        <f>E8*G8</f>
+        <f t="shared" si="1"/>
         <v>4080</v>
       </c>
       <c r="G8" s="19">
@@ -1596,7 +1683,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B9" s="18" t="str">
         <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A9,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
@@ -1606,14 +1693,14 @@
         <v>50</v>
       </c>
       <c r="D9" s="7">
-        <f>C9*G9</f>
+        <f t="shared" si="0"/>
         <v>900</v>
       </c>
       <c r="E9" s="6">
         <v>100</v>
       </c>
       <c r="F9" s="7">
-        <f>E9*G9</f>
+        <f t="shared" si="1"/>
         <v>1800</v>
       </c>
       <c r="G9" s="19">
@@ -1623,7 +1710,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B10" s="18" t="str">
         <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A10,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
@@ -1633,14 +1720,14 @@
         <v>40</v>
       </c>
       <c r="D10" s="7">
-        <f>C10*G10</f>
+        <f t="shared" si="0"/>
         <v>1120</v>
       </c>
       <c r="E10" s="6">
         <v>80</v>
       </c>
       <c r="F10" s="7">
-        <f>E10*G10</f>
+        <f t="shared" si="1"/>
         <v>2240</v>
       </c>
       <c r="G10" s="19">
@@ -1650,7 +1737,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B11" s="18" t="str">
         <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A11,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
@@ -1660,14 +1747,14 @@
         <v>25</v>
       </c>
       <c r="D11" s="7">
-        <f>C11*G11</f>
+        <f t="shared" si="0"/>
         <v>400</v>
       </c>
       <c r="E11" s="6">
         <v>50</v>
       </c>
       <c r="F11" s="7">
-        <f>E11*G11</f>
+        <f t="shared" si="1"/>
         <v>800</v>
       </c>
       <c r="G11" s="19">
@@ -1677,7 +1764,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B12" s="18" t="str">
         <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A12,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
@@ -1687,14 +1774,14 @@
         <v>10</v>
       </c>
       <c r="D12" s="7">
-        <f>C12*G12</f>
+        <f t="shared" si="0"/>
         <v>200</v>
       </c>
       <c r="E12" s="6">
         <v>20</v>
       </c>
       <c r="F12" s="7">
-        <f>E12*G12</f>
+        <f t="shared" si="1"/>
         <v>400</v>
       </c>
       <c r="G12" s="19">
@@ -1704,7 +1791,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B13" s="18" t="str">
         <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A13,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
@@ -1714,14 +1801,14 @@
         <v>35</v>
       </c>
       <c r="D13" s="7">
-        <f>C13*G13</f>
+        <f t="shared" si="0"/>
         <v>509.64606181455633</v>
       </c>
       <c r="E13" s="6">
         <v>70</v>
       </c>
       <c r="F13" s="7">
-        <f>E13*G13</f>
+        <f t="shared" si="1"/>
         <v>1019.2921236291127</v>
       </c>
       <c r="G13" s="19">
@@ -1731,7 +1818,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B14" s="18" t="str">
         <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A14,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
@@ -1741,14 +1828,14 @@
         <v>1</v>
       </c>
       <c r="D14" s="7">
-        <f>C14*G14</f>
+        <f t="shared" si="0"/>
         <v>1000</v>
       </c>
       <c r="E14" s="6">
         <v>0</v>
       </c>
       <c r="F14" s="7">
-        <f>E14*G14</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="19">
@@ -1758,7 +1845,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B15" s="18" t="str">
         <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A15,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
@@ -1768,14 +1855,14 @@
         <v>0</v>
       </c>
       <c r="D15" s="7">
-        <f>C15*G15</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E15" s="6">
         <v>1</v>
       </c>
       <c r="F15" s="7">
-        <f>E15*G15</f>
+        <f t="shared" si="1"/>
         <v>1500</v>
       </c>
       <c r="G15" s="19">
@@ -1785,10 +1872,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="C16" s="9">
         <f>SUMIF(B6:B15,"g",C6:C15)</f>
@@ -1809,7 +1896,7 @@
     </row>
     <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
@@ -1820,35 +1907,35 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C21" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="E21" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="F21" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="G21" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B22" s="18" t="str">
         <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A22,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
@@ -1858,14 +1945,14 @@
         <v>250</v>
       </c>
       <c r="D22" s="7">
-        <f>C22*G22</f>
+        <f t="shared" ref="D22:D31" si="2">C22*G22</f>
         <v>727.27272727272725</v>
       </c>
       <c r="E22" s="6">
         <v>500</v>
       </c>
       <c r="F22" s="7">
-        <f>E22*G22</f>
+        <f t="shared" ref="F22:F31" si="3">E22*G22</f>
         <v>1454.5454545454545</v>
       </c>
       <c r="G22" s="19">
@@ -1875,7 +1962,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B23" s="18" t="str">
         <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A23,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
@@ -1885,14 +1972,14 @@
         <v>1</v>
       </c>
       <c r="D23" s="7">
-        <f>C23*G23</f>
+        <f t="shared" si="2"/>
         <v>500</v>
       </c>
       <c r="E23" s="6">
         <v>2</v>
       </c>
       <c r="F23" s="7">
-        <f>E23*G23</f>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
       <c r="G23" s="19">
@@ -1902,7 +1989,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B24" s="18" t="str">
         <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A24,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
@@ -1912,14 +1999,14 @@
         <v>80</v>
       </c>
       <c r="D24" s="7">
-        <f>C24*G24</f>
+        <f t="shared" si="2"/>
         <v>2720</v>
       </c>
       <c r="E24" s="6">
         <v>160</v>
       </c>
       <c r="F24" s="7">
-        <f>E24*G24</f>
+        <f t="shared" si="3"/>
         <v>5440</v>
       </c>
       <c r="G24" s="19">
@@ -1929,7 +2016,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B25" s="18" t="str">
         <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A25,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
@@ -1939,14 +2026,14 @@
         <v>50</v>
       </c>
       <c r="D25" s="7">
-        <f>C25*G25</f>
+        <f t="shared" si="2"/>
         <v>1500</v>
       </c>
       <c r="E25" s="6">
         <v>100</v>
       </c>
       <c r="F25" s="7">
-        <f>E25*G25</f>
+        <f t="shared" si="3"/>
         <v>3000</v>
       </c>
       <c r="G25" s="19">
@@ -1956,7 +2043,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B26" s="18" t="str">
         <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A26,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
@@ -1966,14 +2053,14 @@
         <v>25</v>
       </c>
       <c r="D26" s="7">
-        <f>C26*G26</f>
+        <f t="shared" si="2"/>
         <v>1000</v>
       </c>
       <c r="E26" s="6">
         <v>50</v>
       </c>
       <c r="F26" s="7">
-        <f>E26*G26</f>
+        <f t="shared" si="3"/>
         <v>2000</v>
       </c>
       <c r="G26" s="19">
@@ -1983,7 +2070,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B27" s="18" t="str">
         <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A27,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
@@ -1993,14 +2080,14 @@
         <v>45</v>
       </c>
       <c r="D27" s="7">
-        <f>C27*G27</f>
+        <f t="shared" si="2"/>
         <v>810</v>
       </c>
       <c r="E27" s="6">
         <v>90</v>
       </c>
       <c r="F27" s="7">
-        <f>E27*G27</f>
+        <f t="shared" si="3"/>
         <v>1620</v>
       </c>
       <c r="G27" s="19">
@@ -2010,7 +2097,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B28" s="18" t="str">
         <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A28,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
@@ -2020,14 +2107,14 @@
         <v>20</v>
       </c>
       <c r="D28" s="7">
-        <f>C28*G28</f>
+        <f t="shared" si="2"/>
         <v>500</v>
       </c>
       <c r="E28" s="6">
         <v>40</v>
       </c>
       <c r="F28" s="7">
-        <f>E28*G28</f>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
       <c r="G28" s="19">
@@ -2037,7 +2124,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B29" s="18" t="str">
         <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A29,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
@@ -2047,14 +2134,14 @@
         <v>40</v>
       </c>
       <c r="D29" s="7">
-        <f>C29*G29</f>
+        <f t="shared" si="2"/>
         <v>582.45264207377863</v>
       </c>
       <c r="E29" s="6">
         <v>80</v>
       </c>
       <c r="F29" s="7">
-        <f>E29*G29</f>
+        <f t="shared" si="3"/>
         <v>1164.9052841475573</v>
       </c>
       <c r="G29" s="19">
@@ -2064,7 +2151,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B30" s="18" t="str">
         <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A30,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
@@ -2074,14 +2161,14 @@
         <v>1</v>
       </c>
       <c r="D30" s="7">
-        <f>C30*G30</f>
+        <f t="shared" si="2"/>
         <v>1000</v>
       </c>
       <c r="E30" s="6">
         <v>0</v>
       </c>
       <c r="F30" s="7">
-        <f>E30*G30</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G30" s="19">
@@ -2091,7 +2178,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B31" s="18" t="str">
         <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A31,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
@@ -2101,14 +2188,14 @@
         <v>0</v>
       </c>
       <c r="D31" s="7">
-        <f>C31*G31</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E31" s="6">
         <v>1</v>
       </c>
       <c r="F31" s="7">
-        <f>E31*G31</f>
+        <f t="shared" si="3"/>
         <v>1500</v>
       </c>
       <c r="G31" s="19">
@@ -2118,10 +2205,10 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="C32" s="9">
         <f>SUMIF(B22:B31,"g",C22:C31)</f>
@@ -2142,7 +2229,7 @@
     </row>
     <row r="35" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B35" s="17"/>
       <c r="C35" s="17"/>
@@ -2153,35 +2240,35 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C37" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="E37" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="F37" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="G37" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B38" s="18" t="str">
         <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A38,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
@@ -2191,14 +2278,14 @@
         <v>200</v>
       </c>
       <c r="D38" s="7">
-        <f>C38*G38</f>
+        <f t="shared" ref="D38:D48" si="4">C38*G38</f>
         <v>1093.0526315789475</v>
       </c>
       <c r="E38" s="6">
         <v>400</v>
       </c>
       <c r="F38" s="7">
-        <f>E38*G38</f>
+        <f t="shared" ref="F38:F48" si="5">E38*G38</f>
         <v>2186.105263157895</v>
       </c>
       <c r="G38" s="19">
@@ -2208,7 +2295,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B39" s="18" t="str">
         <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A39,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
@@ -2218,14 +2305,14 @@
         <v>150</v>
       </c>
       <c r="D39" s="7">
-        <f>C39*G39</f>
+        <f t="shared" si="4"/>
         <v>436.36363636363637</v>
       </c>
       <c r="E39" s="6">
         <v>300</v>
       </c>
       <c r="F39" s="7">
-        <f>E39*G39</f>
+        <f t="shared" si="5"/>
         <v>872.72727272727275</v>
       </c>
       <c r="G39" s="19">
@@ -2235,7 +2322,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B40" s="18" t="str">
         <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A40,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
@@ -2245,14 +2332,14 @@
         <v>1</v>
       </c>
       <c r="D40" s="7">
-        <f>C40*G40</f>
+        <f t="shared" si="4"/>
         <v>500</v>
       </c>
       <c r="E40" s="6">
         <v>2</v>
       </c>
       <c r="F40" s="7">
-        <f>E40*G40</f>
+        <f t="shared" si="5"/>
         <v>1000</v>
       </c>
       <c r="G40" s="19">
@@ -2262,7 +2349,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B41" s="18" t="str">
         <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A41,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
@@ -2272,14 +2359,14 @@
         <v>60</v>
       </c>
       <c r="D41" s="7">
-        <f>C41*G41</f>
+        <f t="shared" si="4"/>
         <v>2040</v>
       </c>
       <c r="E41" s="6">
         <v>120</v>
       </c>
       <c r="F41" s="7">
-        <f>E41*G41</f>
+        <f t="shared" si="5"/>
         <v>4080</v>
       </c>
       <c r="G41" s="19">
@@ -2289,7 +2376,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B42" s="18" t="str">
         <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A42,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
@@ -2299,14 +2386,14 @@
         <v>60</v>
       </c>
       <c r="D42" s="7">
-        <f>C42*G42</f>
+        <f t="shared" si="4"/>
         <v>1680</v>
       </c>
       <c r="E42" s="6">
         <v>120</v>
       </c>
       <c r="F42" s="7">
-        <f>E42*G42</f>
+        <f t="shared" si="5"/>
         <v>3360</v>
       </c>
       <c r="G42" s="19">
@@ -2316,7 +2403,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B43" s="18" t="str">
         <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A43,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
@@ -2326,14 +2413,14 @@
         <v>40</v>
       </c>
       <c r="D43" s="7">
-        <f>C43*G43</f>
+        <f t="shared" si="4"/>
         <v>1800</v>
       </c>
       <c r="E43" s="6">
         <v>80</v>
       </c>
       <c r="F43" s="7">
-        <f>E43*G43</f>
+        <f t="shared" si="5"/>
         <v>3600</v>
       </c>
       <c r="G43" s="19">
@@ -2343,7 +2430,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B44" s="18" t="str">
         <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A44,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
@@ -2353,14 +2440,14 @@
         <v>30</v>
       </c>
       <c r="D44" s="7">
-        <f>C44*G44</f>
+        <f t="shared" si="4"/>
         <v>840</v>
       </c>
       <c r="E44" s="6">
         <v>60</v>
       </c>
       <c r="F44" s="7">
-        <f>E44*G44</f>
+        <f t="shared" si="5"/>
         <v>1680</v>
       </c>
       <c r="G44" s="19">
@@ -2370,7 +2457,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B45" s="18" t="str">
         <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A45,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
@@ -2380,14 +2467,14 @@
         <v>30</v>
       </c>
       <c r="D45" s="7">
-        <f>C45*G45</f>
+        <f t="shared" si="4"/>
         <v>360</v>
       </c>
       <c r="E45" s="6">
         <v>60</v>
       </c>
       <c r="F45" s="7">
-        <f>E45*G45</f>
+        <f t="shared" si="5"/>
         <v>720</v>
       </c>
       <c r="G45" s="19">
@@ -2397,7 +2484,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B46" s="18" t="str">
         <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A46,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
@@ -2407,14 +2494,14 @@
         <v>40</v>
       </c>
       <c r="D46" s="7">
-        <f>C46*G46</f>
+        <f t="shared" si="4"/>
         <v>582.45264207377863</v>
       </c>
       <c r="E46" s="6">
         <v>80</v>
       </c>
       <c r="F46" s="7">
-        <f>E46*G46</f>
+        <f t="shared" si="5"/>
         <v>1164.9052841475573</v>
       </c>
       <c r="G46" s="19">
@@ -2424,7 +2511,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B47" s="18" t="str">
         <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A47,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
@@ -2434,14 +2521,14 @@
         <v>1</v>
       </c>
       <c r="D47" s="7">
-        <f>C47*G47</f>
+        <f t="shared" si="4"/>
         <v>1000</v>
       </c>
       <c r="E47" s="6">
         <v>0</v>
       </c>
       <c r="F47" s="7">
-        <f>E47*G47</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G47" s="19">
@@ -2451,7 +2538,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B48" s="18" t="str">
         <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A48,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
@@ -2461,14 +2548,14 @@
         <v>0</v>
       </c>
       <c r="D48" s="7">
-        <f>C48*G48</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E48" s="6">
         <v>1</v>
       </c>
       <c r="F48" s="7">
-        <f>E48*G48</f>
+        <f t="shared" si="5"/>
         <v>1500</v>
       </c>
       <c r="G48" s="19">
@@ -2476,12 +2563,12 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="C49" s="9">
         <f>SUMIF(B38:B48,"g",C38:C48)</f>
@@ -2498,6 +2585,258 @@
       <c r="F49" s="10">
         <f>SUM(F38:F48)</f>
         <v>20163.737820032726</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A52" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="B52" s="17"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="17"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="17"/>
+      <c r="G52" s="17"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B55" s="18" t="str">
+        <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A55,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
+        <v>g</v>
+      </c>
+      <c r="C55" s="6">
+        <v>250</v>
+      </c>
+      <c r="D55" s="7">
+        <f>C55*G55</f>
+        <v>727.27272727272725</v>
+      </c>
+      <c r="E55" s="6">
+        <v>500</v>
+      </c>
+      <c r="F55" s="7">
+        <f>E55*G55</f>
+        <v>1454.5454545454545</v>
+      </c>
+      <c r="G55" s="19">
+        <f>INDEX(Insumos!$E$5:$E$25,MATCH(A55,Insumos!$A$5:$A$25,0))</f>
+        <v>2.9090909090909092</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B56" s="18" t="str">
+        <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A56,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
+        <v>und</v>
+      </c>
+      <c r="C56" s="6">
+        <v>1</v>
+      </c>
+      <c r="D56" s="7">
+        <f>C56*G56</f>
+        <v>500</v>
+      </c>
+      <c r="E56" s="6">
+        <v>2</v>
+      </c>
+      <c r="F56" s="7">
+        <f>E56*G56</f>
+        <v>1000</v>
+      </c>
+      <c r="G56" s="19">
+        <f>INDEX(Insumos!$E$5:$E$25,MATCH(A56,Insumos!$A$5:$A$25,0))</f>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B57" s="18" t="str">
+        <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A57,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
+        <v>g</v>
+      </c>
+      <c r="C57" s="6">
+        <v>45</v>
+      </c>
+      <c r="D57" s="7">
+        <f>C57*G57</f>
+        <v>1260</v>
+      </c>
+      <c r="E57" s="6">
+        <v>90</v>
+      </c>
+      <c r="F57" s="7">
+        <f>E57*G57</f>
+        <v>2520</v>
+      </c>
+      <c r="G57" s="19">
+        <f>INDEX(Insumos!$E$5:$E$25,MATCH(A57,Insumos!$A$5:$A$25,0))</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B58" s="18" t="str">
+        <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A58,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
+        <v>g</v>
+      </c>
+      <c r="C58" s="6">
+        <v>20</v>
+      </c>
+      <c r="D58" s="7">
+        <f>C58*G58</f>
+        <v>800</v>
+      </c>
+      <c r="E58" s="6">
+        <v>40</v>
+      </c>
+      <c r="F58" s="7">
+        <f>E58*G58</f>
+        <v>1600</v>
+      </c>
+      <c r="G58" s="19">
+        <f>INDEX(Insumos!$E$5:$E$25,MATCH(A58,Insumos!$A$5:$A$25,0))</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B59" s="18" t="str">
+        <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A59,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
+        <v>g</v>
+      </c>
+      <c r="C59" s="6">
+        <v>35</v>
+      </c>
+      <c r="D59" s="7">
+        <f>C59*G59</f>
+        <v>509.64606181455633</v>
+      </c>
+      <c r="E59" s="6">
+        <v>70</v>
+      </c>
+      <c r="F59" s="7">
+        <f>E59*G59</f>
+        <v>1019.2921236291127</v>
+      </c>
+      <c r="G59" s="19">
+        <f>INDEX(Insumos!$E$5:$E$25,MATCH(A59,Insumos!$A$5:$A$25,0))</f>
+        <v>14.561316051844466</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B60" s="18" t="str">
+        <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A60,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
+        <v>und</v>
+      </c>
+      <c r="C60" s="6">
+        <v>1</v>
+      </c>
+      <c r="D60" s="7">
+        <f>C60*G60</f>
+        <v>1000</v>
+      </c>
+      <c r="E60" s="6">
+        <v>0</v>
+      </c>
+      <c r="F60" s="7">
+        <f>E60*G60</f>
+        <v>0</v>
+      </c>
+      <c r="G60" s="19">
+        <f>INDEX(Insumos!$E$5:$E$25,MATCH(A60,Insumos!$A$5:$A$25,0))</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B61" s="18" t="str">
+        <f>IF(INDEX(Insumos!$B$5:$B$25,MATCH(A61,Insumos!$A$5:$A$25,0))="kg","g","und")</f>
+        <v>und</v>
+      </c>
+      <c r="C61" s="6">
+        <v>0</v>
+      </c>
+      <c r="D61" s="7">
+        <f>C61*G61</f>
+        <v>0</v>
+      </c>
+      <c r="E61" s="6">
+        <v>1</v>
+      </c>
+      <c r="F61" s="7">
+        <f>E61*G61</f>
+        <v>1500</v>
+      </c>
+      <c r="G61" s="19">
+        <f>INDEX(Insumos!$E$5:$E$25,MATCH(A61,Insumos!$A$5:$A$25,0))</f>
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C62" s="9">
+        <f>SUMIF(B55:B61,"g",C55:C61)</f>
+        <v>350</v>
+      </c>
+      <c r="D62" s="10">
+        <f>SUM(D55:D61)</f>
+        <v>4796.9187890872836</v>
+      </c>
+      <c r="E62" s="9">
+        <f>SUMIF(B55:B61,"g",E55:E61)</f>
+        <v>700</v>
+      </c>
+      <c r="F62" s="10">
+        <f>SUM(F55:F61)</f>
+        <v>9093.8375781745672</v>
       </c>
     </row>
   </sheetData>
@@ -2521,40 +2860,40 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="C5" s="8">
         <v>1600</v>
@@ -2563,19 +2902,19 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="E5" s="14">
-        <f>IF(D5=0,0,IF(B5="kg",C5/1000/D5,C5/D5))</f>
+        <f t="shared" ref="E5:E25" si="0">IF(D5=0,0,IF(B5="kg",C5/1000/D5,C5/D5))</f>
         <v>2.9090909090909092</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C6" s="8">
         <v>5192</v>
@@ -2584,19 +2923,19 @@
         <v>0.95</v>
       </c>
       <c r="E6" s="14">
-        <f>IF(D6=0,0,IF(B6="kg",C6/1000/D6,C6/D6))</f>
+        <f t="shared" si="0"/>
         <v>5.4652631578947375</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C7" s="8">
         <v>17000</v>
@@ -2605,19 +2944,19 @@
         <v>0.5</v>
       </c>
       <c r="E7" s="14">
-        <f>IF(D7=0,0,IF(B7="kg",C7/1000/D7,C7/D7))</f>
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C8" s="8">
         <v>18000</v>
@@ -2626,19 +2965,19 @@
         <v>1</v>
       </c>
       <c r="E8" s="14">
-        <f>IF(D8=0,0,IF(B8="kg",C8/1000/D8,C8/D8))</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C9" s="8">
         <v>28000</v>
@@ -2647,19 +2986,19 @@
         <v>1</v>
       </c>
       <c r="E9" s="14">
-        <f>IF(D9=0,0,IF(B9="kg",C9/1000/D9,C9/D9))</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C10" s="8">
         <v>40000</v>
@@ -2668,19 +3007,19 @@
         <v>1</v>
       </c>
       <c r="E10" s="14">
-        <f>IF(D10=0,0,IF(B10="kg",C10/1000/D10,C10/D10))</f>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C11" s="8">
         <v>28000</v>
@@ -2689,19 +3028,19 @@
         <v>1</v>
       </c>
       <c r="E11" s="14">
-        <f>IF(D11=0,0,IF(B11="kg",C11/1000/D11,C11/D11))</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C12" s="8">
         <v>45000</v>
@@ -2710,19 +3049,19 @@
         <v>1</v>
       </c>
       <c r="E12" s="14">
-        <f>IF(D12=0,0,IF(B12="kg",C12/1000/D12,C12/D12))</f>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C13" s="8">
         <v>30000</v>
@@ -2731,19 +3070,19 @@
         <v>1</v>
       </c>
       <c r="E13" s="14">
-        <f>IF(D13=0,0,IF(B13="kg",C13/1000/D13,C13/D13))</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C14" s="8">
         <v>16000</v>
@@ -2752,19 +3091,19 @@
         <v>1</v>
       </c>
       <c r="E14" s="14">
-        <f>IF(D14=0,0,IF(B14="kg",C14/1000/D14,C14/D14))</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C15" s="8">
         <v>12000</v>
@@ -2773,19 +3112,19 @@
         <v>1</v>
       </c>
       <c r="E15" s="14">
-        <f>IF(D15=0,0,IF(B15="kg",C15/1000/D15,C15/D15))</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C16" s="8">
         <v>20000</v>
@@ -2794,19 +3133,19 @@
         <v>1</v>
       </c>
       <c r="E16" s="14">
-        <f>IF(D16=0,0,IF(B16="kg",C16/1000/D16,C16/D16))</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C17" s="8">
         <v>18000</v>
@@ -2815,19 +3154,19 @@
         <v>1</v>
       </c>
       <c r="E17" s="14">
-        <f>IF(D17=0,0,IF(B17="kg",C17/1000/D17,C17/D17))</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C18" s="8">
         <v>25000</v>
@@ -2836,19 +3175,19 @@
         <v>1</v>
       </c>
       <c r="E18" s="14">
-        <f>IF(D18=0,0,IF(B18="kg",C18/1000/D18,C18/D18))</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C19" s="8">
         <v>3500</v>
@@ -2857,19 +3196,19 @@
         <v>0.5</v>
       </c>
       <c r="E19" s="14">
-        <f>IF(D19=0,0,IF(B19="kg",C19/1000/D19,C19/D19))</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C20" s="15">
         <f>'Salsa Carnitas'!D16</f>
@@ -2879,19 +3218,19 @@
         <v>1</v>
       </c>
       <c r="E20" s="14">
-        <f>IF(D20=0,0,IF(B20="kg",C20/1000/D20,C20/D20))</f>
+        <f t="shared" si="0"/>
         <v>14.561316051844466</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="C21" s="8">
         <v>500</v>
@@ -2900,19 +3239,19 @@
         <v>1</v>
       </c>
       <c r="E21" s="14">
-        <f>IF(D21=0,0,IF(B21="kg",C21/1000/D21,C21/D21))</f>
+        <f t="shared" si="0"/>
         <v>500</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C22" s="8">
         <v>1000</v>
@@ -2921,19 +3260,19 @@
         <v>1</v>
       </c>
       <c r="E22" s="14">
-        <f>IF(D22=0,0,IF(B22="kg",C22/1000/D22,C22/D22))</f>
+        <f t="shared" si="0"/>
         <v>1000</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C23" s="8">
         <v>1500</v>
@@ -2942,19 +3281,19 @@
         <v>1</v>
       </c>
       <c r="E23" s="14">
-        <f>IF(D23=0,0,IF(B23="kg",C23/1000/D23,C23/D23))</f>
+        <f t="shared" si="0"/>
         <v>1500</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C24" s="8">
         <v>1300</v>
@@ -2963,19 +3302,19 @@
         <v>1</v>
       </c>
       <c r="E24" s="14">
-        <f>IF(D24=0,0,IF(B24="kg",C24/1000/D24,C24/D24))</f>
+        <f t="shared" si="0"/>
         <v>1300</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C25" s="8">
         <v>1800</v>
@@ -2984,11 +3323,11 @@
         <v>1</v>
       </c>
       <c r="E25" s="14">
-        <f>IF(D25=0,0,IF(B25="kg",C25/1000/D25,C25/D25))</f>
+        <f t="shared" si="0"/>
         <v>1800</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -3011,29 +3350,29 @@
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B4" s="6">
         <v>840</v>
@@ -3042,16 +3381,16 @@
         <v>13000</v>
       </c>
       <c r="D4" s="7">
-        <f>B4*C4/1000</f>
+        <f t="shared" ref="D4:D14" si="0">B4*C4/1000</f>
         <v>10920</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B5" s="6">
         <v>70</v>
@@ -3060,16 +3399,16 @@
         <v>25000</v>
       </c>
       <c r="D5" s="7">
-        <f>B5*C5/1000</f>
+        <f t="shared" si="0"/>
         <v>1750</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" s="6">
         <v>25</v>
@@ -3078,16 +3417,16 @@
         <v>8000</v>
       </c>
       <c r="D6" s="7">
-        <f>B6*C6/1000</f>
+        <f t="shared" si="0"/>
         <v>200</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B7" s="6">
         <v>25</v>
@@ -3096,16 +3435,16 @@
         <v>15000</v>
       </c>
       <c r="D7" s="7">
-        <f>B7*C7/1000</f>
+        <f t="shared" si="0"/>
         <v>375</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B8" s="6">
         <v>12</v>
@@ -3114,16 +3453,16 @@
         <v>5000</v>
       </c>
       <c r="D8" s="7">
-        <f>B8*C8/1000</f>
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B9" s="6">
         <v>10</v>
@@ -3132,16 +3471,16 @@
         <v>0</v>
       </c>
       <c r="D9" s="7">
-        <f>B9*C9/1000</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B10" s="6">
         <v>8</v>
@@ -3150,16 +3489,16 @@
         <v>80000</v>
       </c>
       <c r="D10" s="7">
-        <f>B10*C10/1000</f>
+        <f t="shared" si="0"/>
         <v>640</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B11" s="6">
         <v>4</v>
@@ -3168,16 +3507,16 @@
         <v>40000</v>
       </c>
       <c r="D11" s="7">
-        <f>B11*C11/1000</f>
+        <f t="shared" si="0"/>
         <v>160</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B12" s="6">
         <v>4</v>
@@ -3186,16 +3525,16 @@
         <v>40000</v>
       </c>
       <c r="D12" s="7">
-        <f>B12*C12/1000</f>
+        <f t="shared" si="0"/>
         <v>160</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B13" s="6">
         <v>3</v>
@@ -3204,16 +3543,16 @@
         <v>80000</v>
       </c>
       <c r="D13" s="7">
-        <f>B13*C13/1000</f>
+        <f t="shared" si="0"/>
         <v>240</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B14" s="6">
         <v>2</v>
@@ -3222,16 +3561,16 @@
         <v>50000</v>
       </c>
       <c r="D14" s="7">
-        <f>B14*C14/1000</f>
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B15" s="9">
         <f>SUM(B4:B14)</f>
@@ -3244,7 +3583,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D16" s="10">
         <f>IF(B15=0,0,D15/B15*1000)</f>
@@ -3273,38 +3612,38 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>134</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C4" s="6">
         <v>50</v>
@@ -3317,20 +3656,20 @@
         <v>5000</v>
       </c>
       <c r="F4" s="12">
-        <f>IF(E4=0,0,D4/E4)</f>
+        <f t="shared" ref="F4:F11" si="0">IF(E4=0,0,D4/E4)</f>
         <v>0.34</v>
       </c>
       <c r="G4" s="7">
-        <f>E4-D4</f>
+        <f t="shared" ref="G4:G11" si="1">E4-D4</f>
         <v>3300</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C5" s="6">
         <v>30</v>
@@ -3343,20 +3682,20 @@
         <v>3500</v>
       </c>
       <c r="F5" s="12">
-        <f>IF(E5=0,0,D5/E5)</f>
+        <f t="shared" si="0"/>
         <v>0.38571428571428573</v>
       </c>
       <c r="G5" s="7">
-        <f>E5-D5</f>
+        <f t="shared" si="1"/>
         <v>2150</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C6" s="6">
         <v>25</v>
@@ -3369,20 +3708,20 @@
         <v>3000</v>
       </c>
       <c r="F6" s="12">
-        <f>IF(E6=0,0,D6/E6)</f>
+        <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="G6" s="7">
-        <f>E6-D6</f>
+        <f t="shared" si="1"/>
         <v>2000</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6">
         <v>50</v>
@@ -3395,20 +3734,20 @@
         <v>2500</v>
       </c>
       <c r="F7" s="12">
-        <f>IF(E7=0,0,D7/E7)</f>
+        <f t="shared" si="0"/>
         <v>0.14000000000000001</v>
       </c>
       <c r="G7" s="7">
-        <f>E7-D7</f>
+        <f t="shared" si="1"/>
         <v>2150</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C8" s="6">
         <v>60</v>
@@ -3421,20 +3760,20 @@
         <v>2000</v>
       </c>
       <c r="F8" s="12">
-        <f>IF(E8=0,0,D8/E8)</f>
+        <f t="shared" si="0"/>
         <v>0.43683948155533397</v>
       </c>
       <c r="G8" s="7">
-        <f>E8-D8</f>
+        <f t="shared" si="1"/>
         <v>1126.3210368893319</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C9" s="6">
         <v>15</v>
@@ -3447,20 +3786,20 @@
         <v>1000</v>
       </c>
       <c r="F9" s="12">
-        <f>IF(E9=0,0,D9/E9)</f>
+        <f t="shared" si="0"/>
         <v>0.375</v>
       </c>
       <c r="G9" s="7">
-        <f>E9-D9</f>
+        <f t="shared" si="1"/>
         <v>625</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="C10" s="6">
         <v>250</v>
@@ -3473,20 +3812,20 @@
         <v>15000</v>
       </c>
       <c r="F10" s="12">
-        <f>IF(E10=0,0,D10/E10)</f>
+        <f t="shared" si="0"/>
         <v>0.3626886008640744</v>
       </c>
       <c r="G10" s="7">
-        <f>E10-D10</f>
+        <f t="shared" si="1"/>
         <v>9559.670987038884</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>145</v>
       </c>
       <c r="C11" s="5">
         <v>1</v>
@@ -3499,42 +3838,42 @@
         <v>21900</v>
       </c>
       <c r="F11" s="12">
-        <f>IF(E11=0,0,D11/E11)</f>
+        <f t="shared" si="0"/>
         <v>0.39711957941037823</v>
       </c>
       <c r="G11" s="7">
-        <f>E11-D11</f>
+        <f t="shared" si="1"/>
         <v>13203.081210912716</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
